--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8102-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8102-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7934A265-61A3-4BE3-ADC1-EC1D63B58817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A29BD17-B411-461F-9587-0EDE7A5ABF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D9883103-D379-44CF-8B87-AB7DC47AFF68}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{524A6CDD-EE1A-411A-BB8B-F55FF4E20771}"/>
   </bookViews>
   <sheets>
     <sheet name="8102-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1454,18 +1454,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BFE37A2-3D76-4C4B-B507-731FB1C78538}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B168F16E-00E0-4BDD-A89B-2BCA82FB3740}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1493,7 +1493,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1619,7 +1619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2013</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2012</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2011</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2010</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2009</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
         <v>37</v>
       </c>
